--- a/examples/outputs/Birgo RR Exhibits - Saddlebrook at Tates Creekv07.05.26.xlsx
+++ b/examples/outputs/Birgo RR Exhibits - Saddlebrook at Tates Creekv07.05.26.xlsx
@@ -15051,32 +15051,32 @@
       </c>
       <c r="AB31" s="67" t="inlineStr">
         <is>
-          <t>Pet Rent</t>
+          <t>conpetrt</t>
         </is>
       </c>
       <c r="AC31" s="67" t="inlineStr">
         <is>
-          <t>Pest</t>
+          <t>conpest</t>
         </is>
       </c>
       <c r="AD31" s="67" t="inlineStr">
         <is>
-          <t>Tech Fee</t>
+          <t>contfinc</t>
         </is>
       </c>
       <c r="AE31" s="67" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>coninsu</t>
         </is>
       </c>
       <c r="AF31" s="67" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>congarg</t>
         </is>
       </c>
       <c r="AG31" s="67" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>conliab</t>
         </is>
       </c>
       <c r="AI31" s="67" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AK31" s="67" t="inlineStr">
         <is>
-          <t>Employee Discount</t>
+          <t>conempl</t>
         </is>
       </c>
     </row>
@@ -15157,11 +15157,11 @@
         <v/>
       </c>
       <c r="S32" s="81">
-        <f>AI32</f>
+        <f>SUM(AI32:AI32)</f>
         <v/>
       </c>
       <c r="T32" s="81">
-        <f>AK32</f>
+        <f>SUM(AK32:AK32)</f>
         <v/>
       </c>
       <c r="Y32" s="81" t="n">
@@ -15245,11 +15245,11 @@
         <v/>
       </c>
       <c r="S33" s="81">
-        <f>AI33</f>
+        <f>SUM(AI33:AI33)</f>
         <v/>
       </c>
       <c r="T33" s="81">
-        <f>AK33</f>
+        <f>SUM(AK33:AK33)</f>
         <v/>
       </c>
       <c r="Y33" s="81" t="n">
@@ -15333,11 +15333,11 @@
         <v/>
       </c>
       <c r="S34" s="81">
-        <f>AI34</f>
+        <f>SUM(AI34:AI34)</f>
         <v/>
       </c>
       <c r="T34" s="81">
-        <f>AK34</f>
+        <f>SUM(AK34:AK34)</f>
         <v/>
       </c>
       <c r="Y34" s="81" t="n">
@@ -15424,11 +15424,11 @@
         <v/>
       </c>
       <c r="S35" s="81">
-        <f>AI35</f>
+        <f>SUM(AI35:AI35)</f>
         <v/>
       </c>
       <c r="T35" s="81">
-        <f>AK35</f>
+        <f>SUM(AK35:AK35)</f>
         <v/>
       </c>
       <c r="Y35" s="81" t="n">
@@ -15515,11 +15515,11 @@
         <v/>
       </c>
       <c r="S36" s="81">
-        <f>AI36</f>
+        <f>SUM(AI36:AI36)</f>
         <v/>
       </c>
       <c r="T36" s="81">
-        <f>AK36</f>
+        <f>SUM(AK36:AK36)</f>
         <v/>
       </c>
       <c r="Y36" s="81" t="n">
@@ -15598,11 +15598,11 @@
         <v/>
       </c>
       <c r="S37" s="85">
-        <f>AI37</f>
+        <f>SUM(AI37:AI37)</f>
         <v/>
       </c>
       <c r="T37" s="85">
-        <f>AK37</f>
+        <f>SUM(AK37:AK37)</f>
         <v/>
       </c>
       <c r="U37" s="86" t="n"/>
@@ -15693,11 +15693,11 @@
         <v/>
       </c>
       <c r="S38" s="81">
-        <f>AI38</f>
+        <f>SUM(AI38:AI38)</f>
         <v/>
       </c>
       <c r="T38" s="81">
-        <f>AK38</f>
+        <f>SUM(AK38:AK38)</f>
         <v/>
       </c>
       <c r="Y38" s="81" t="n">
@@ -15776,11 +15776,11 @@
         <v/>
       </c>
       <c r="S39" s="85">
-        <f>AI39</f>
+        <f>SUM(AI39:AI39)</f>
         <v/>
       </c>
       <c r="T39" s="85">
-        <f>AK39</f>
+        <f>SUM(AK39:AK39)</f>
         <v/>
       </c>
       <c r="U39" s="86" t="n"/>
@@ -15874,11 +15874,11 @@
         <v/>
       </c>
       <c r="S40" s="81">
-        <f>AI40</f>
+        <f>SUM(AI40:AI40)</f>
         <v/>
       </c>
       <c r="T40" s="81">
-        <f>AK40</f>
+        <f>SUM(AK40:AK40)</f>
         <v/>
       </c>
       <c r="Y40" s="81" t="n">
@@ -15968,11 +15968,11 @@
         <v/>
       </c>
       <c r="S41" s="81">
-        <f>AI41</f>
+        <f>SUM(AI41:AI41)</f>
         <v/>
       </c>
       <c r="T41" s="81">
-        <f>AK41</f>
+        <f>SUM(AK41:AK41)</f>
         <v/>
       </c>
       <c r="Y41" s="81" t="n">
@@ -16065,11 +16065,11 @@
         <v/>
       </c>
       <c r="S42" s="81">
-        <f>AI42</f>
+        <f>SUM(AI42:AI42)</f>
         <v/>
       </c>
       <c r="T42" s="81">
-        <f>AK42</f>
+        <f>SUM(AK42:AK42)</f>
         <v/>
       </c>
       <c r="Y42" s="81" t="n">
@@ -16156,11 +16156,11 @@
         <v/>
       </c>
       <c r="S43" s="81">
-        <f>AI43</f>
+        <f>SUM(AI43:AI43)</f>
         <v/>
       </c>
       <c r="T43" s="81">
-        <f>AK43</f>
+        <f>SUM(AK43:AK43)</f>
         <v/>
       </c>
       <c r="Y43" s="81" t="n">
@@ -16247,11 +16247,11 @@
         <v/>
       </c>
       <c r="S44" s="81">
-        <f>AI44</f>
+        <f>SUM(AI44:AI44)</f>
         <v/>
       </c>
       <c r="T44" s="81">
-        <f>AK44</f>
+        <f>SUM(AK44:AK44)</f>
         <v/>
       </c>
       <c r="Y44" s="81" t="n">
@@ -16335,11 +16335,11 @@
         <v/>
       </c>
       <c r="S45" s="81">
-        <f>AI45</f>
+        <f>SUM(AI45:AI45)</f>
         <v/>
       </c>
       <c r="T45" s="81">
-        <f>AK45</f>
+        <f>SUM(AK45:AK45)</f>
         <v/>
       </c>
       <c r="Y45" s="81" t="n">
@@ -16423,11 +16423,11 @@
         <v/>
       </c>
       <c r="S46" s="81">
-        <f>AI46</f>
+        <f>SUM(AI46:AI46)</f>
         <v/>
       </c>
       <c r="T46" s="81">
-        <f>AK46</f>
+        <f>SUM(AK46:AK46)</f>
         <v/>
       </c>
       <c r="Y46" s="81" t="n">
@@ -16514,11 +16514,11 @@
         <v/>
       </c>
       <c r="S47" s="81">
-        <f>AI47</f>
+        <f>SUM(AI47:AI47)</f>
         <v/>
       </c>
       <c r="T47" s="81">
-        <f>AK47</f>
+        <f>SUM(AK47:AK47)</f>
         <v/>
       </c>
       <c r="Y47" s="81" t="n">
@@ -16608,11 +16608,11 @@
         <v/>
       </c>
       <c r="S48" s="81">
-        <f>AI48</f>
+        <f>SUM(AI48:AI48)</f>
         <v/>
       </c>
       <c r="T48" s="81">
-        <f>AK48</f>
+        <f>SUM(AK48:AK48)</f>
         <v/>
       </c>
       <c r="Y48" s="81" t="n">
@@ -16699,11 +16699,11 @@
         <v/>
       </c>
       <c r="S49" s="81">
-        <f>AI49</f>
+        <f>SUM(AI49:AI49)</f>
         <v/>
       </c>
       <c r="T49" s="81">
-        <f>AK49</f>
+        <f>SUM(AK49:AK49)</f>
         <v/>
       </c>
       <c r="Y49" s="81" t="n">
@@ -16790,11 +16790,11 @@
         <v/>
       </c>
       <c r="S50" s="81">
-        <f>AI50</f>
+        <f>SUM(AI50:AI50)</f>
         <v/>
       </c>
       <c r="T50" s="81">
-        <f>AK50</f>
+        <f>SUM(AK50:AK50)</f>
         <v/>
       </c>
       <c r="Y50" s="81" t="n">
@@ -16878,11 +16878,11 @@
         <v/>
       </c>
       <c r="S51" s="81">
-        <f>AI51</f>
+        <f>SUM(AI51:AI51)</f>
         <v/>
       </c>
       <c r="T51" s="81">
-        <f>AK51</f>
+        <f>SUM(AK51:AK51)</f>
         <v/>
       </c>
       <c r="Y51" s="81" t="n">
@@ -16969,11 +16969,11 @@
         <v/>
       </c>
       <c r="S52" s="81">
-        <f>AI52</f>
+        <f>SUM(AI52:AI52)</f>
         <v/>
       </c>
       <c r="T52" s="81">
-        <f>AK52</f>
+        <f>SUM(AK52:AK52)</f>
         <v/>
       </c>
       <c r="Y52" s="81" t="n">
@@ -17060,11 +17060,11 @@
         <v/>
       </c>
       <c r="S53" s="81">
-        <f>AI53</f>
+        <f>SUM(AI53:AI53)</f>
         <v/>
       </c>
       <c r="T53" s="81">
-        <f>AK53</f>
+        <f>SUM(AK53:AK53)</f>
         <v/>
       </c>
       <c r="Y53" s="81" t="n">
@@ -17148,11 +17148,11 @@
         <v/>
       </c>
       <c r="S54" s="81">
-        <f>AI54</f>
+        <f>SUM(AI54:AI54)</f>
         <v/>
       </c>
       <c r="T54" s="81">
-        <f>AK54</f>
+        <f>SUM(AK54:AK54)</f>
         <v/>
       </c>
       <c r="Y54" s="81" t="n">
@@ -17236,11 +17236,11 @@
         <v/>
       </c>
       <c r="S55" s="81">
-        <f>AI55</f>
+        <f>SUM(AI55:AI55)</f>
         <v/>
       </c>
       <c r="T55" s="81">
-        <f>AK55</f>
+        <f>SUM(AK55:AK55)</f>
         <v/>
       </c>
       <c r="Y55" s="81" t="n">
@@ -17324,11 +17324,11 @@
         <v/>
       </c>
       <c r="S56" s="81">
-        <f>AI56</f>
+        <f>SUM(AI56:AI56)</f>
         <v/>
       </c>
       <c r="T56" s="81">
-        <f>AK56</f>
+        <f>SUM(AK56:AK56)</f>
         <v/>
       </c>
       <c r="Y56" s="81" t="n">
@@ -17415,11 +17415,11 @@
         <v/>
       </c>
       <c r="S57" s="81">
-        <f>AI57</f>
+        <f>SUM(AI57:AI57)</f>
         <v/>
       </c>
       <c r="T57" s="81">
-        <f>AK57</f>
+        <f>SUM(AK57:AK57)</f>
         <v/>
       </c>
       <c r="Y57" s="81" t="n">
@@ -17503,11 +17503,11 @@
         <v/>
       </c>
       <c r="S58" s="81">
-        <f>AI58</f>
+        <f>SUM(AI58:AI58)</f>
         <v/>
       </c>
       <c r="T58" s="81">
-        <f>AK58</f>
+        <f>SUM(AK58:AK58)</f>
         <v/>
       </c>
       <c r="Y58" s="81" t="n">
@@ -17594,11 +17594,11 @@
         <v/>
       </c>
       <c r="S59" s="81">
-        <f>AI59</f>
+        <f>SUM(AI59:AI59)</f>
         <v/>
       </c>
       <c r="T59" s="81">
-        <f>AK59</f>
+        <f>SUM(AK59:AK59)</f>
         <v/>
       </c>
       <c r="Y59" s="81" t="n">
@@ -17683,11 +17683,11 @@
         <v/>
       </c>
       <c r="S60" s="85">
-        <f>AI60</f>
+        <f>SUM(AI60:AI60)</f>
         <v/>
       </c>
       <c r="T60" s="85">
-        <f>AK60</f>
+        <f>SUM(AK60:AK60)</f>
         <v/>
       </c>
       <c r="U60" s="86" t="n"/>
@@ -17778,11 +17778,11 @@
         <v/>
       </c>
       <c r="S61" s="81">
-        <f>AI61</f>
+        <f>SUM(AI61:AI61)</f>
         <v/>
       </c>
       <c r="T61" s="81">
-        <f>AK61</f>
+        <f>SUM(AK61:AK61)</f>
         <v/>
       </c>
       <c r="Y61" s="81" t="n">
@@ -17869,11 +17869,11 @@
         <v/>
       </c>
       <c r="S62" s="81">
-        <f>AI62</f>
+        <f>SUM(AI62:AI62)</f>
         <v/>
       </c>
       <c r="T62" s="81">
-        <f>AK62</f>
+        <f>SUM(AK62:AK62)</f>
         <v/>
       </c>
       <c r="Y62" s="81" t="n">
@@ -17952,11 +17952,11 @@
         <v/>
       </c>
       <c r="S63" s="85">
-        <f>AI63</f>
+        <f>SUM(AI63:AI63)</f>
         <v/>
       </c>
       <c r="T63" s="85">
-        <f>AK63</f>
+        <f>SUM(AK63:AK63)</f>
         <v/>
       </c>
       <c r="U63" s="86" t="n"/>
@@ -18047,11 +18047,11 @@
         <v/>
       </c>
       <c r="S64" s="81">
-        <f>AI64</f>
+        <f>SUM(AI64:AI64)</f>
         <v/>
       </c>
       <c r="T64" s="81">
-        <f>AK64</f>
+        <f>SUM(AK64:AK64)</f>
         <v/>
       </c>
       <c r="Y64" s="81" t="n">
@@ -18138,11 +18138,11 @@
         <v/>
       </c>
       <c r="S65" s="81">
-        <f>AI65</f>
+        <f>SUM(AI65:AI65)</f>
         <v/>
       </c>
       <c r="T65" s="81">
-        <f>AK65</f>
+        <f>SUM(AK65:AK65)</f>
         <v/>
       </c>
       <c r="Y65" s="81" t="n">
@@ -18226,11 +18226,11 @@
         <v/>
       </c>
       <c r="S66" s="81">
-        <f>AI66</f>
+        <f>SUM(AI66:AI66)</f>
         <v/>
       </c>
       <c r="T66" s="81">
-        <f>AK66</f>
+        <f>SUM(AK66:AK66)</f>
         <v/>
       </c>
       <c r="Y66" s="81" t="n">
@@ -18320,11 +18320,11 @@
         <v/>
       </c>
       <c r="S67" s="81">
-        <f>AI67</f>
+        <f>SUM(AI67:AI67)</f>
         <v/>
       </c>
       <c r="T67" s="81">
-        <f>AK67</f>
+        <f>SUM(AK67:AK67)</f>
         <v/>
       </c>
       <c r="Y67" s="81" t="n">
@@ -18408,11 +18408,11 @@
         <v/>
       </c>
       <c r="S68" s="81">
-        <f>AI68</f>
+        <f>SUM(AI68:AI68)</f>
         <v/>
       </c>
       <c r="T68" s="81">
-        <f>AK68</f>
+        <f>SUM(AK68:AK68)</f>
         <v/>
       </c>
       <c r="Y68" s="81" t="n">
@@ -18496,11 +18496,11 @@
         <v/>
       </c>
       <c r="S69" s="81">
-        <f>AI69</f>
+        <f>SUM(AI69:AI69)</f>
         <v/>
       </c>
       <c r="T69" s="81">
-        <f>AK69</f>
+        <f>SUM(AK69:AK69)</f>
         <v/>
       </c>
       <c r="Y69" s="81" t="n">
@@ -18584,11 +18584,11 @@
         <v/>
       </c>
       <c r="S70" s="81">
-        <f>AI70</f>
+        <f>SUM(AI70:AI70)</f>
         <v/>
       </c>
       <c r="T70" s="81">
-        <f>AK70</f>
+        <f>SUM(AK70:AK70)</f>
         <v/>
       </c>
       <c r="Y70" s="81" t="n">
@@ -18672,11 +18672,11 @@
         <v/>
       </c>
       <c r="S71" s="81">
-        <f>AI71</f>
+        <f>SUM(AI71:AI71)</f>
         <v/>
       </c>
       <c r="T71" s="81">
-        <f>AK71</f>
+        <f>SUM(AK71:AK71)</f>
         <v/>
       </c>
       <c r="Y71" s="81" t="n">
@@ -18760,11 +18760,11 @@
         <v/>
       </c>
       <c r="S72" s="81">
-        <f>AI72</f>
+        <f>SUM(AI72:AI72)</f>
         <v/>
       </c>
       <c r="T72" s="81">
-        <f>AK72</f>
+        <f>SUM(AK72:AK72)</f>
         <v/>
       </c>
       <c r="Y72" s="81" t="n">
@@ -18851,11 +18851,11 @@
         <v/>
       </c>
       <c r="S73" s="81">
-        <f>AI73</f>
+        <f>SUM(AI73:AI73)</f>
         <v/>
       </c>
       <c r="T73" s="81">
-        <f>AK73</f>
+        <f>SUM(AK73:AK73)</f>
         <v/>
       </c>
       <c r="Y73" s="81" t="n">
@@ -18939,11 +18939,11 @@
         <v/>
       </c>
       <c r="S74" s="81">
-        <f>AI74</f>
+        <f>SUM(AI74:AI74)</f>
         <v/>
       </c>
       <c r="T74" s="81">
-        <f>AK74</f>
+        <f>SUM(AK74:AK74)</f>
         <v/>
       </c>
       <c r="Y74" s="81" t="n">
@@ -19030,11 +19030,11 @@
         <v/>
       </c>
       <c r="S75" s="81">
-        <f>AI75</f>
+        <f>SUM(AI75:AI75)</f>
         <v/>
       </c>
       <c r="T75" s="81">
-        <f>AK75</f>
+        <f>SUM(AK75:AK75)</f>
         <v/>
       </c>
       <c r="Y75" s="81" t="n">
@@ -19118,11 +19118,11 @@
         <v/>
       </c>
       <c r="S76" s="81">
-        <f>AI76</f>
+        <f>SUM(AI76:AI76)</f>
         <v/>
       </c>
       <c r="T76" s="81">
-        <f>AK76</f>
+        <f>SUM(AK76:AK76)</f>
         <v/>
       </c>
       <c r="Y76" s="81" t="n">
@@ -19209,11 +19209,11 @@
         <v/>
       </c>
       <c r="S77" s="81">
-        <f>AI77</f>
+        <f>SUM(AI77:AI77)</f>
         <v/>
       </c>
       <c r="T77" s="81">
-        <f>AK77</f>
+        <f>SUM(AK77:AK77)</f>
         <v/>
       </c>
       <c r="Y77" s="81" t="n">
@@ -19300,11 +19300,11 @@
         <v/>
       </c>
       <c r="S78" s="81">
-        <f>AI78</f>
+        <f>SUM(AI78:AI78)</f>
         <v/>
       </c>
       <c r="T78" s="81">
-        <f>AK78</f>
+        <f>SUM(AK78:AK78)</f>
         <v/>
       </c>
       <c r="Y78" s="81" t="n">
@@ -19391,11 +19391,11 @@
         <v/>
       </c>
       <c r="S79" s="81">
-        <f>AI79</f>
+        <f>SUM(AI79:AI79)</f>
         <v/>
       </c>
       <c r="T79" s="81">
-        <f>AK79</f>
+        <f>SUM(AK79:AK79)</f>
         <v/>
       </c>
       <c r="Y79" s="81" t="n">
@@ -19477,11 +19477,11 @@
         <v/>
       </c>
       <c r="S80" s="85">
-        <f>AI80</f>
+        <f>SUM(AI80:AI80)</f>
         <v/>
       </c>
       <c r="T80" s="85">
-        <f>AK80</f>
+        <f>SUM(AK80:AK80)</f>
         <v/>
       </c>
       <c r="U80" s="86" t="n"/>
@@ -19572,11 +19572,11 @@
         <v/>
       </c>
       <c r="S81" s="81">
-        <f>AI81</f>
+        <f>SUM(AI81:AI81)</f>
         <v/>
       </c>
       <c r="T81" s="81">
-        <f>AK81</f>
+        <f>SUM(AK81:AK81)</f>
         <v/>
       </c>
       <c r="Y81" s="81" t="n">
@@ -19660,11 +19660,11 @@
         <v/>
       </c>
       <c r="S82" s="81">
-        <f>AI82</f>
+        <f>SUM(AI82:AI82)</f>
         <v/>
       </c>
       <c r="T82" s="81">
-        <f>AK82</f>
+        <f>SUM(AK82:AK82)</f>
         <v/>
       </c>
       <c r="Y82" s="81" t="n">
@@ -19748,11 +19748,11 @@
         <v/>
       </c>
       <c r="S83" s="81">
-        <f>AI83</f>
+        <f>SUM(AI83:AI83)</f>
         <v/>
       </c>
       <c r="T83" s="81">
-        <f>AK83</f>
+        <f>SUM(AK83:AK83)</f>
         <v/>
       </c>
       <c r="Y83" s="81" t="n">
@@ -19839,11 +19839,11 @@
         <v/>
       </c>
       <c r="S84" s="81">
-        <f>AI84</f>
+        <f>SUM(AI84:AI84)</f>
         <v/>
       </c>
       <c r="T84" s="81">
-        <f>AK84</f>
+        <f>SUM(AK84:AK84)</f>
         <v/>
       </c>
       <c r="Y84" s="81" t="n">
@@ -19930,11 +19930,11 @@
         <v/>
       </c>
       <c r="S85" s="81">
-        <f>AI85</f>
+        <f>SUM(AI85:AI85)</f>
         <v/>
       </c>
       <c r="T85" s="81">
-        <f>AK85</f>
+        <f>SUM(AK85:AK85)</f>
         <v/>
       </c>
       <c r="Y85" s="81" t="n">
@@ -20021,11 +20021,11 @@
         <v/>
       </c>
       <c r="S86" s="81">
-        <f>AI86</f>
+        <f>SUM(AI86:AI86)</f>
         <v/>
       </c>
       <c r="T86" s="81">
-        <f>AK86</f>
+        <f>SUM(AK86:AK86)</f>
         <v/>
       </c>
       <c r="Y86" s="81" t="n">
@@ -20112,11 +20112,11 @@
         <v/>
       </c>
       <c r="S87" s="81">
-        <f>AI87</f>
+        <f>SUM(AI87:AI87)</f>
         <v/>
       </c>
       <c r="T87" s="81">
-        <f>AK87</f>
+        <f>SUM(AK87:AK87)</f>
         <v/>
       </c>
       <c r="Y87" s="81" t="n">
@@ -20200,11 +20200,11 @@
         <v/>
       </c>
       <c r="S88" s="81">
-        <f>AI88</f>
+        <f>SUM(AI88:AI88)</f>
         <v/>
       </c>
       <c r="T88" s="81">
-        <f>AK88</f>
+        <f>SUM(AK88:AK88)</f>
         <v/>
       </c>
       <c r="Y88" s="81" t="n">
@@ -20294,11 +20294,11 @@
         <v/>
       </c>
       <c r="S89" s="81">
-        <f>AI89</f>
+        <f>SUM(AI89:AI89)</f>
         <v/>
       </c>
       <c r="T89" s="81">
-        <f>AK89</f>
+        <f>SUM(AK89:AK89)</f>
         <v/>
       </c>
       <c r="Y89" s="81" t="n">
@@ -20385,11 +20385,11 @@
         <v/>
       </c>
       <c r="S90" s="81">
-        <f>AI90</f>
+        <f>SUM(AI90:AI90)</f>
         <v/>
       </c>
       <c r="T90" s="81">
-        <f>AK90</f>
+        <f>SUM(AK90:AK90)</f>
         <v/>
       </c>
       <c r="Y90" s="81" t="n">
@@ -20473,11 +20473,11 @@
         <v/>
       </c>
       <c r="S91" s="81">
-        <f>AI91</f>
+        <f>SUM(AI91:AI91)</f>
         <v/>
       </c>
       <c r="T91" s="81">
-        <f>AK91</f>
+        <f>SUM(AK91:AK91)</f>
         <v/>
       </c>
       <c r="Y91" s="81" t="n">
@@ -20561,11 +20561,11 @@
         <v/>
       </c>
       <c r="S92" s="81">
-        <f>AI92</f>
+        <f>SUM(AI92:AI92)</f>
         <v/>
       </c>
       <c r="T92" s="81">
-        <f>AK92</f>
+        <f>SUM(AK92:AK92)</f>
         <v/>
       </c>
       <c r="Y92" s="81" t="n">
@@ -20652,11 +20652,11 @@
         <v/>
       </c>
       <c r="S93" s="81">
-        <f>AI93</f>
+        <f>SUM(AI93:AI93)</f>
         <v/>
       </c>
       <c r="T93" s="81">
-        <f>AK93</f>
+        <f>SUM(AK93:AK93)</f>
         <v/>
       </c>
       <c r="Y93" s="81" t="n">
@@ -20743,11 +20743,11 @@
         <v/>
       </c>
       <c r="S94" s="81">
-        <f>AI94</f>
+        <f>SUM(AI94:AI94)</f>
         <v/>
       </c>
       <c r="T94" s="81">
-        <f>AK94</f>
+        <f>SUM(AK94:AK94)</f>
         <v/>
       </c>
       <c r="Y94" s="81" t="n">
@@ -20831,11 +20831,11 @@
         <v/>
       </c>
       <c r="S95" s="81">
-        <f>AI95</f>
+        <f>SUM(AI95:AI95)</f>
         <v/>
       </c>
       <c r="T95" s="81">
-        <f>AK95</f>
+        <f>SUM(AK95:AK95)</f>
         <v/>
       </c>
       <c r="Y95" s="81" t="n">
@@ -20928,11 +20928,11 @@
         <v/>
       </c>
       <c r="S96" s="81">
-        <f>AI96</f>
+        <f>SUM(AI96:AI96)</f>
         <v/>
       </c>
       <c r="T96" s="81">
-        <f>AK96</f>
+        <f>SUM(AK96:AK96)</f>
         <v/>
       </c>
       <c r="Y96" s="81" t="n">
@@ -21016,11 +21016,11 @@
         <v/>
       </c>
       <c r="S97" s="81">
-        <f>AI97</f>
+        <f>SUM(AI97:AI97)</f>
         <v/>
       </c>
       <c r="T97" s="81">
-        <f>AK97</f>
+        <f>SUM(AK97:AK97)</f>
         <v/>
       </c>
       <c r="Y97" s="81" t="n">
@@ -21104,11 +21104,11 @@
         <v/>
       </c>
       <c r="S98" s="81">
-        <f>AI98</f>
+        <f>SUM(AI98:AI98)</f>
         <v/>
       </c>
       <c r="T98" s="81">
-        <f>AK98</f>
+        <f>SUM(AK98:AK98)</f>
         <v/>
       </c>
       <c r="Y98" s="81" t="n">
@@ -21198,11 +21198,11 @@
         <v/>
       </c>
       <c r="S99" s="81">
-        <f>AI99</f>
+        <f>SUM(AI99:AI99)</f>
         <v/>
       </c>
       <c r="T99" s="81">
-        <f>AK99</f>
+        <f>SUM(AK99:AK99)</f>
         <v/>
       </c>
       <c r="Y99" s="81" t="n">
@@ -21286,11 +21286,11 @@
         <v/>
       </c>
       <c r="S100" s="81">
-        <f>AI100</f>
+        <f>SUM(AI100:AI100)</f>
         <v/>
       </c>
       <c r="T100" s="81">
-        <f>AK100</f>
+        <f>SUM(AK100:AK100)</f>
         <v/>
       </c>
       <c r="Y100" s="81" t="n">
@@ -21377,11 +21377,11 @@
         <v/>
       </c>
       <c r="S101" s="81">
-        <f>AI101</f>
+        <f>SUM(AI101:AI101)</f>
         <v/>
       </c>
       <c r="T101" s="81">
-        <f>AK101</f>
+        <f>SUM(AK101:AK101)</f>
         <v/>
       </c>
       <c r="Y101" s="81" t="n">
@@ -21468,11 +21468,11 @@
         <v/>
       </c>
       <c r="S102" s="81">
-        <f>AI102</f>
+        <f>SUM(AI102:AI102)</f>
         <v/>
       </c>
       <c r="T102" s="81">
-        <f>AK102</f>
+        <f>SUM(AK102:AK102)</f>
         <v/>
       </c>
       <c r="Y102" s="81" t="n">
@@ -21556,11 +21556,11 @@
         <v/>
       </c>
       <c r="S103" s="81">
-        <f>AI103</f>
+        <f>SUM(AI103:AI103)</f>
         <v/>
       </c>
       <c r="T103" s="81">
-        <f>AK103</f>
+        <f>SUM(AK103:AK103)</f>
         <v/>
       </c>
       <c r="Y103" s="81" t="n">
@@ -21650,11 +21650,11 @@
         <v/>
       </c>
       <c r="S104" s="81">
-        <f>AI104</f>
+        <f>SUM(AI104:AI104)</f>
         <v/>
       </c>
       <c r="T104" s="81">
-        <f>AK104</f>
+        <f>SUM(AK104:AK104)</f>
         <v/>
       </c>
       <c r="Y104" s="81" t="n">
@@ -21741,11 +21741,11 @@
         <v/>
       </c>
       <c r="S105" s="81">
-        <f>AI105</f>
+        <f>SUM(AI105:AI105)</f>
         <v/>
       </c>
       <c r="T105" s="81">
-        <f>AK105</f>
+        <f>SUM(AK105:AK105)</f>
         <v/>
       </c>
       <c r="Y105" s="81" t="n">
@@ -21832,11 +21832,11 @@
         <v/>
       </c>
       <c r="S106" s="81">
-        <f>AI106</f>
+        <f>SUM(AI106:AI106)</f>
         <v/>
       </c>
       <c r="T106" s="81">
-        <f>AK106</f>
+        <f>SUM(AK106:AK106)</f>
         <v/>
       </c>
       <c r="Y106" s="81" t="n">
@@ -21926,11 +21926,11 @@
         <v/>
       </c>
       <c r="S107" s="81">
-        <f>AI107</f>
+        <f>SUM(AI107:AI107)</f>
         <v/>
       </c>
       <c r="T107" s="81">
-        <f>AK107</f>
+        <f>SUM(AK107:AK107)</f>
         <v/>
       </c>
       <c r="Y107" s="81" t="n">
@@ -22017,11 +22017,11 @@
         <v/>
       </c>
       <c r="S108" s="81">
-        <f>AI108</f>
+        <f>SUM(AI108:AI108)</f>
         <v/>
       </c>
       <c r="T108" s="81">
-        <f>AK108</f>
+        <f>SUM(AK108:AK108)</f>
         <v/>
       </c>
       <c r="Y108" s="81" t="n">
@@ -22105,11 +22105,11 @@
         <v/>
       </c>
       <c r="S109" s="81">
-        <f>AI109</f>
+        <f>SUM(AI109:AI109)</f>
         <v/>
       </c>
       <c r="T109" s="81">
-        <f>AK109</f>
+        <f>SUM(AK109:AK109)</f>
         <v/>
       </c>
       <c r="Y109" s="81" t="n">
@@ -22196,11 +22196,11 @@
         <v/>
       </c>
       <c r="S110" s="81">
-        <f>AI110</f>
+        <f>SUM(AI110:AI110)</f>
         <v/>
       </c>
       <c r="T110" s="81">
-        <f>AK110</f>
+        <f>SUM(AK110:AK110)</f>
         <v/>
       </c>
       <c r="Y110" s="81" t="n">
@@ -22287,11 +22287,11 @@
         <v/>
       </c>
       <c r="S111" s="81">
-        <f>AI111</f>
+        <f>SUM(AI111:AI111)</f>
         <v/>
       </c>
       <c r="T111" s="81">
-        <f>AK111</f>
+        <f>SUM(AK111:AK111)</f>
         <v/>
       </c>
       <c r="Y111" s="81" t="n">
@@ -22378,11 +22378,11 @@
         <v/>
       </c>
       <c r="S112" s="81">
-        <f>AI112</f>
+        <f>SUM(AI112:AI112)</f>
         <v/>
       </c>
       <c r="T112" s="81">
-        <f>AK112</f>
+        <f>SUM(AK112:AK112)</f>
         <v/>
       </c>
       <c r="Y112" s="81" t="n">
@@ -22472,11 +22472,11 @@
         <v/>
       </c>
       <c r="S113" s="81">
-        <f>AI113</f>
+        <f>SUM(AI113:AI113)</f>
         <v/>
       </c>
       <c r="T113" s="81">
-        <f>AK113</f>
+        <f>SUM(AK113:AK113)</f>
         <v/>
       </c>
       <c r="Y113" s="81" t="n">
@@ -22560,11 +22560,11 @@
         <v/>
       </c>
       <c r="S114" s="81">
-        <f>AI114</f>
+        <f>SUM(AI114:AI114)</f>
         <v/>
       </c>
       <c r="T114" s="81">
-        <f>AK114</f>
+        <f>SUM(AK114:AK114)</f>
         <v/>
       </c>
       <c r="Y114" s="81" t="n">
@@ -22648,11 +22648,11 @@
         <v/>
       </c>
       <c r="S115" s="81">
-        <f>AI115</f>
+        <f>SUM(AI115:AI115)</f>
         <v/>
       </c>
       <c r="T115" s="81">
-        <f>AK115</f>
+        <f>SUM(AK115:AK115)</f>
         <v/>
       </c>
       <c r="Y115" s="81" t="n">
@@ -22736,11 +22736,11 @@
         <v/>
       </c>
       <c r="S116" s="81">
-        <f>AI116</f>
+        <f>SUM(AI116:AI116)</f>
         <v/>
       </c>
       <c r="T116" s="81">
-        <f>AK116</f>
+        <f>SUM(AK116:AK116)</f>
         <v/>
       </c>
       <c r="Y116" s="81" t="n">
@@ -22830,11 +22830,11 @@
         <v/>
       </c>
       <c r="S117" s="81">
-        <f>AI117</f>
+        <f>SUM(AI117:AI117)</f>
         <v/>
       </c>
       <c r="T117" s="81">
-        <f>AK117</f>
+        <f>SUM(AK117:AK117)</f>
         <v/>
       </c>
       <c r="Y117" s="81" t="n">
@@ -22921,11 +22921,11 @@
         <v/>
       </c>
       <c r="S118" s="81">
-        <f>AI118</f>
+        <f>SUM(AI118:AI118)</f>
         <v/>
       </c>
       <c r="T118" s="81">
-        <f>AK118</f>
+        <f>SUM(AK118:AK118)</f>
         <v/>
       </c>
       <c r="Y118" s="81" t="n">
@@ -23009,11 +23009,11 @@
         <v/>
       </c>
       <c r="S119" s="81">
-        <f>AI119</f>
+        <f>SUM(AI119:AI119)</f>
         <v/>
       </c>
       <c r="T119" s="81">
-        <f>AK119</f>
+        <f>SUM(AK119:AK119)</f>
         <v/>
       </c>
       <c r="Y119" s="81" t="n">
@@ -23103,11 +23103,11 @@
         <v/>
       </c>
       <c r="S120" s="81">
-        <f>AI120</f>
+        <f>SUM(AI120:AI120)</f>
         <v/>
       </c>
       <c r="T120" s="81">
-        <f>AK120</f>
+        <f>SUM(AK120:AK120)</f>
         <v/>
       </c>
       <c r="Y120" s="81" t="n">
@@ -23191,11 +23191,11 @@
         <v/>
       </c>
       <c r="S121" s="81">
-        <f>AI121</f>
+        <f>SUM(AI121:AI121)</f>
         <v/>
       </c>
       <c r="T121" s="81">
-        <f>AK121</f>
+        <f>SUM(AK121:AK121)</f>
         <v/>
       </c>
       <c r="Y121" s="81" t="n">
@@ -23285,11 +23285,11 @@
         <v/>
       </c>
       <c r="S122" s="81">
-        <f>AI122</f>
+        <f>SUM(AI122:AI122)</f>
         <v/>
       </c>
       <c r="T122" s="81">
-        <f>AK122</f>
+        <f>SUM(AK122:AK122)</f>
         <v/>
       </c>
       <c r="Y122" s="81" t="n">
@@ -23367,11 +23367,11 @@
         <v/>
       </c>
       <c r="S123" s="81">
-        <f>AI123</f>
+        <f>SUM(AI123:AI123)</f>
         <v/>
       </c>
       <c r="T123" s="81">
-        <f>AK123</f>
+        <f>SUM(AK123:AK123)</f>
         <v/>
       </c>
       <c r="Y123" s="81" t="n">
@@ -23452,11 +23452,11 @@
         <v/>
       </c>
       <c r="S124" s="81">
-        <f>AI124</f>
+        <f>SUM(AI124:AI124)</f>
         <v/>
       </c>
       <c r="T124" s="81">
-        <f>AK124</f>
+        <f>SUM(AK124:AK124)</f>
         <v/>
       </c>
       <c r="Y124" s="81" t="n">
@@ -23535,11 +23535,11 @@
         <v/>
       </c>
       <c r="S125" s="85">
-        <f>AI125</f>
+        <f>SUM(AI125:AI125)</f>
         <v/>
       </c>
       <c r="T125" s="85">
-        <f>AK125</f>
+        <f>SUM(AK125:AK125)</f>
         <v/>
       </c>
       <c r="U125" s="86" t="n"/>
@@ -23630,11 +23630,11 @@
         <v/>
       </c>
       <c r="S126" s="81">
-        <f>AI126</f>
+        <f>SUM(AI126:AI126)</f>
         <v/>
       </c>
       <c r="T126" s="81">
-        <f>AK126</f>
+        <f>SUM(AK126:AK126)</f>
         <v/>
       </c>
       <c r="Y126" s="81" t="n">
@@ -23721,11 +23721,11 @@
         <v/>
       </c>
       <c r="S127" s="81">
-        <f>AI127</f>
+        <f>SUM(AI127:AI127)</f>
         <v/>
       </c>
       <c r="T127" s="81">
-        <f>AK127</f>
+        <f>SUM(AK127:AK127)</f>
         <v/>
       </c>
       <c r="Y127" s="81" t="n">
@@ -23809,11 +23809,11 @@
         <v/>
       </c>
       <c r="S128" s="81">
-        <f>AI128</f>
+        <f>SUM(AI128:AI128)</f>
         <v/>
       </c>
       <c r="T128" s="81">
-        <f>AK128</f>
+        <f>SUM(AK128:AK128)</f>
         <v/>
       </c>
       <c r="Y128" s="81" t="n">
@@ -23900,11 +23900,11 @@
         <v/>
       </c>
       <c r="S129" s="81">
-        <f>AI129</f>
+        <f>SUM(AI129:AI129)</f>
         <v/>
       </c>
       <c r="T129" s="81">
-        <f>AK129</f>
+        <f>SUM(AK129:AK129)</f>
         <v/>
       </c>
       <c r="Y129" s="81" t="n">
@@ -23994,11 +23994,11 @@
         <v/>
       </c>
       <c r="S130" s="81">
-        <f>AI130</f>
+        <f>SUM(AI130:AI130)</f>
         <v/>
       </c>
       <c r="T130" s="81">
-        <f>AK130</f>
+        <f>SUM(AK130:AK130)</f>
         <v/>
       </c>
       <c r="Y130" s="81" t="n">
@@ -24082,11 +24082,11 @@
         <v/>
       </c>
       <c r="S131" s="81">
-        <f>AI131</f>
+        <f>SUM(AI131:AI131)</f>
         <v/>
       </c>
       <c r="T131" s="81">
-        <f>AK131</f>
+        <f>SUM(AK131:AK131)</f>
         <v/>
       </c>
       <c r="Y131" s="81" t="n">
@@ -24173,11 +24173,11 @@
         <v/>
       </c>
       <c r="S132" s="81">
-        <f>AI132</f>
+        <f>SUM(AI132:AI132)</f>
         <v/>
       </c>
       <c r="T132" s="81">
-        <f>AK132</f>
+        <f>SUM(AK132:AK132)</f>
         <v/>
       </c>
       <c r="Y132" s="81" t="n">
@@ -24267,11 +24267,11 @@
         <v/>
       </c>
       <c r="S133" s="81">
-        <f>AI133</f>
+        <f>SUM(AI133:AI133)</f>
         <v/>
       </c>
       <c r="T133" s="81">
-        <f>AK133</f>
+        <f>SUM(AK133:AK133)</f>
         <v/>
       </c>
       <c r="Y133" s="81" t="n">
@@ -24355,11 +24355,11 @@
         <v/>
       </c>
       <c r="S134" s="81">
-        <f>AI134</f>
+        <f>SUM(AI134:AI134)</f>
         <v/>
       </c>
       <c r="T134" s="81">
-        <f>AK134</f>
+        <f>SUM(AK134:AK134)</f>
         <v/>
       </c>
       <c r="Y134" s="81" t="n">
@@ -24446,11 +24446,11 @@
         <v/>
       </c>
       <c r="S135" s="81">
-        <f>AI135</f>
+        <f>SUM(AI135:AI135)</f>
         <v/>
       </c>
       <c r="T135" s="81">
-        <f>AK135</f>
+        <f>SUM(AK135:AK135)</f>
         <v/>
       </c>
       <c r="Y135" s="81" t="n">
@@ -24534,11 +24534,11 @@
         <v/>
       </c>
       <c r="S136" s="81">
-        <f>AI136</f>
+        <f>SUM(AI136:AI136)</f>
         <v/>
       </c>
       <c r="T136" s="81">
-        <f>AK136</f>
+        <f>SUM(AK136:AK136)</f>
         <v/>
       </c>
       <c r="Y136" s="81" t="n">
@@ -24631,11 +24631,11 @@
         <v/>
       </c>
       <c r="S137" s="81">
-        <f>AI137</f>
+        <f>SUM(AI137:AI137)</f>
         <v/>
       </c>
       <c r="T137" s="81">
-        <f>AK137</f>
+        <f>SUM(AK137:AK137)</f>
         <v/>
       </c>
       <c r="Y137" s="81" t="n">
@@ -24722,11 +24722,11 @@
         <v/>
       </c>
       <c r="S138" s="81">
-        <f>AI138</f>
+        <f>SUM(AI138:AI138)</f>
         <v/>
       </c>
       <c r="T138" s="81">
-        <f>AK138</f>
+        <f>SUM(AK138:AK138)</f>
         <v/>
       </c>
       <c r="Y138" s="81" t="n">
@@ -24813,11 +24813,11 @@
         <v/>
       </c>
       <c r="S139" s="81">
-        <f>AI139</f>
+        <f>SUM(AI139:AI139)</f>
         <v/>
       </c>
       <c r="T139" s="81">
-        <f>AK139</f>
+        <f>SUM(AK139:AK139)</f>
         <v/>
       </c>
       <c r="Y139" s="81" t="n">
@@ -24904,11 +24904,11 @@
         <v/>
       </c>
       <c r="S140" s="81">
-        <f>AI140</f>
+        <f>SUM(AI140:AI140)</f>
         <v/>
       </c>
       <c r="T140" s="81">
-        <f>AK140</f>
+        <f>SUM(AK140:AK140)</f>
         <v/>
       </c>
       <c r="Y140" s="81" t="n">
@@ -24992,11 +24992,11 @@
         <v/>
       </c>
       <c r="S141" s="81">
-        <f>AI141</f>
+        <f>SUM(AI141:AI141)</f>
         <v/>
       </c>
       <c r="T141" s="81">
-        <f>AK141</f>
+        <f>SUM(AK141:AK141)</f>
         <v/>
       </c>
       <c r="Y141" s="81" t="n">
@@ -25083,11 +25083,11 @@
         <v/>
       </c>
       <c r="S142" s="81">
-        <f>AI142</f>
+        <f>SUM(AI142:AI142)</f>
         <v/>
       </c>
       <c r="T142" s="81">
-        <f>AK142</f>
+        <f>SUM(AK142:AK142)</f>
         <v/>
       </c>
       <c r="Y142" s="81" t="n">
@@ -25171,11 +25171,11 @@
         <v/>
       </c>
       <c r="S143" s="81">
-        <f>AI143</f>
+        <f>SUM(AI143:AI143)</f>
         <v/>
       </c>
       <c r="T143" s="81">
-        <f>AK143</f>
+        <f>SUM(AK143:AK143)</f>
         <v/>
       </c>
       <c r="Y143" s="81" t="n">
@@ -25265,11 +25265,11 @@
         <v/>
       </c>
       <c r="S144" s="81">
-        <f>AI144</f>
+        <f>SUM(AI144:AI144)</f>
         <v/>
       </c>
       <c r="T144" s="81">
-        <f>AK144</f>
+        <f>SUM(AK144:AK144)</f>
         <v/>
       </c>
       <c r="Y144" s="81" t="n">
@@ -25362,11 +25362,11 @@
         <v/>
       </c>
       <c r="S145" s="81">
-        <f>AI145</f>
+        <f>SUM(AI145:AI145)</f>
         <v/>
       </c>
       <c r="T145" s="81">
-        <f>AK145</f>
+        <f>SUM(AK145:AK145)</f>
         <v/>
       </c>
       <c r="Y145" s="81" t="n">
@@ -25453,11 +25453,11 @@
         <v/>
       </c>
       <c r="S146" s="81">
-        <f>AI146</f>
+        <f>SUM(AI146:AI146)</f>
         <v/>
       </c>
       <c r="T146" s="81">
-        <f>AK146</f>
+        <f>SUM(AK146:AK146)</f>
         <v/>
       </c>
       <c r="Y146" s="81" t="n">
@@ -25541,11 +25541,11 @@
         <v/>
       </c>
       <c r="S147" s="81">
-        <f>AI147</f>
+        <f>SUM(AI147:AI147)</f>
         <v/>
       </c>
       <c r="T147" s="81">
-        <f>AK147</f>
+        <f>SUM(AK147:AK147)</f>
         <v/>
       </c>
       <c r="Y147" s="81" t="n">
@@ -25632,11 +25632,11 @@
         <v/>
       </c>
       <c r="S148" s="81">
-        <f>AI148</f>
+        <f>SUM(AI148:AI148)</f>
         <v/>
       </c>
       <c r="T148" s="81">
-        <f>AK148</f>
+        <f>SUM(AK148:AK148)</f>
         <v/>
       </c>
       <c r="Y148" s="81" t="n">
@@ -25723,11 +25723,11 @@
         <v/>
       </c>
       <c r="S149" s="81">
-        <f>AI149</f>
+        <f>SUM(AI149:AI149)</f>
         <v/>
       </c>
       <c r="T149" s="81">
-        <f>AK149</f>
+        <f>SUM(AK149:AK149)</f>
         <v/>
       </c>
       <c r="Y149" s="81" t="n">
@@ -25814,11 +25814,11 @@
         <v/>
       </c>
       <c r="S150" s="81">
-        <f>AI150</f>
+        <f>SUM(AI150:AI150)</f>
         <v/>
       </c>
       <c r="T150" s="81">
-        <f>AK150</f>
+        <f>SUM(AK150:AK150)</f>
         <v/>
       </c>
       <c r="Y150" s="81" t="n">
@@ -25902,11 +25902,11 @@
         <v/>
       </c>
       <c r="S151" s="81">
-        <f>AI151</f>
+        <f>SUM(AI151:AI151)</f>
         <v/>
       </c>
       <c r="T151" s="81">
-        <f>AK151</f>
+        <f>SUM(AK151:AK151)</f>
         <v/>
       </c>
       <c r="Y151" s="81" t="n">
@@ -25990,11 +25990,11 @@
         <v/>
       </c>
       <c r="S152" s="81">
-        <f>AI152</f>
+        <f>SUM(AI152:AI152)</f>
         <v/>
       </c>
       <c r="T152" s="81">
-        <f>AK152</f>
+        <f>SUM(AK152:AK152)</f>
         <v/>
       </c>
       <c r="Y152" s="81" t="n">
@@ -26081,11 +26081,11 @@
         <v/>
       </c>
       <c r="S153" s="81">
-        <f>AI153</f>
+        <f>SUM(AI153:AI153)</f>
         <v/>
       </c>
       <c r="T153" s="81">
-        <f>AK153</f>
+        <f>SUM(AK153:AK153)</f>
         <v/>
       </c>
       <c r="Y153" s="81" t="n">
@@ -26169,11 +26169,11 @@
         <v/>
       </c>
       <c r="S154" s="81">
-        <f>AI154</f>
+        <f>SUM(AI154:AI154)</f>
         <v/>
       </c>
       <c r="T154" s="81">
-        <f>AK154</f>
+        <f>SUM(AK154:AK154)</f>
         <v/>
       </c>
       <c r="Y154" s="81" t="n">
@@ -26263,11 +26263,11 @@
         <v/>
       </c>
       <c r="S155" s="81">
-        <f>AI155</f>
+        <f>SUM(AI155:AI155)</f>
         <v/>
       </c>
       <c r="T155" s="81">
-        <f>AK155</f>
+        <f>SUM(AK155:AK155)</f>
         <v/>
       </c>
       <c r="Y155" s="81" t="n">
@@ -26357,11 +26357,11 @@
         <v/>
       </c>
       <c r="S156" s="81">
-        <f>AI156</f>
+        <f>SUM(AI156:AI156)</f>
         <v/>
       </c>
       <c r="T156" s="81">
-        <f>AK156</f>
+        <f>SUM(AK156:AK156)</f>
         <v/>
       </c>
       <c r="Y156" s="81" t="n">
@@ -26445,11 +26445,11 @@
         <v/>
       </c>
       <c r="S157" s="81">
-        <f>AI157</f>
+        <f>SUM(AI157:AI157)</f>
         <v/>
       </c>
       <c r="T157" s="81">
-        <f>AK157</f>
+        <f>SUM(AK157:AK157)</f>
         <v/>
       </c>
       <c r="Y157" s="81" t="n">
@@ -26536,11 +26536,11 @@
         <v/>
       </c>
       <c r="S158" s="81">
-        <f>AI158</f>
+        <f>SUM(AI158:AI158)</f>
         <v/>
       </c>
       <c r="T158" s="81">
-        <f>AK158</f>
+        <f>SUM(AK158:AK158)</f>
         <v/>
       </c>
       <c r="Y158" s="81" t="n">
@@ -26624,11 +26624,11 @@
         <v/>
       </c>
       <c r="S159" s="81">
-        <f>AI159</f>
+        <f>SUM(AI159:AI159)</f>
         <v/>
       </c>
       <c r="T159" s="81">
-        <f>AK159</f>
+        <f>SUM(AK159:AK159)</f>
         <v/>
       </c>
       <c r="Y159" s="81" t="n">
@@ -26713,11 +26713,11 @@
         <v/>
       </c>
       <c r="S160" s="85">
-        <f>AI160</f>
+        <f>SUM(AI160:AI160)</f>
         <v/>
       </c>
       <c r="T160" s="85">
-        <f>AK160</f>
+        <f>SUM(AK160:AK160)</f>
         <v/>
       </c>
       <c r="U160" s="86" t="n"/>
@@ -26808,11 +26808,11 @@
         <v/>
       </c>
       <c r="S161" s="81">
-        <f>AI161</f>
+        <f>SUM(AI161:AI161)</f>
         <v/>
       </c>
       <c r="T161" s="81">
-        <f>AK161</f>
+        <f>SUM(AK161:AK161)</f>
         <v/>
       </c>
       <c r="Y161" s="81" t="n">
@@ -26899,11 +26899,11 @@
         <v/>
       </c>
       <c r="S162" s="81">
-        <f>AI162</f>
+        <f>SUM(AI162:AI162)</f>
         <v/>
       </c>
       <c r="T162" s="81">
-        <f>AK162</f>
+        <f>SUM(AK162:AK162)</f>
         <v/>
       </c>
       <c r="Y162" s="81" t="n">
@@ -26987,11 +26987,11 @@
         <v/>
       </c>
       <c r="S163" s="81">
-        <f>AI163</f>
+        <f>SUM(AI163:AI163)</f>
         <v/>
       </c>
       <c r="T163" s="81">
-        <f>AK163</f>
+        <f>SUM(AK163:AK163)</f>
         <v/>
       </c>
       <c r="Y163" s="81" t="n">
@@ -27081,11 +27081,11 @@
         <v/>
       </c>
       <c r="S164" s="81">
-        <f>AI164</f>
+        <f>SUM(AI164:AI164)</f>
         <v/>
       </c>
       <c r="T164" s="81">
-        <f>AK164</f>
+        <f>SUM(AK164:AK164)</f>
         <v/>
       </c>
       <c r="Y164" s="81" t="n">
@@ -27169,11 +27169,11 @@
         <v/>
       </c>
       <c r="S165" s="81">
-        <f>AI165</f>
+        <f>SUM(AI165:AI165)</f>
         <v/>
       </c>
       <c r="T165" s="81">
-        <f>AK165</f>
+        <f>SUM(AK165:AK165)</f>
         <v/>
       </c>
       <c r="Y165" s="81" t="n">
@@ -27260,11 +27260,11 @@
         <v/>
       </c>
       <c r="S166" s="81">
-        <f>AI166</f>
+        <f>SUM(AI166:AI166)</f>
         <v/>
       </c>
       <c r="T166" s="81">
-        <f>AK166</f>
+        <f>SUM(AK166:AK166)</f>
         <v/>
       </c>
       <c r="Y166" s="81" t="n">
@@ -27346,11 +27346,11 @@
         <v/>
       </c>
       <c r="S167" s="85">
-        <f>AI167</f>
+        <f>SUM(AI167:AI167)</f>
         <v/>
       </c>
       <c r="T167" s="85">
-        <f>AK167</f>
+        <f>SUM(AK167:AK167)</f>
         <v/>
       </c>
       <c r="U167" s="86" t="n"/>
@@ -27444,11 +27444,11 @@
         <v/>
       </c>
       <c r="S168" s="81">
-        <f>AI168</f>
+        <f>SUM(AI168:AI168)</f>
         <v/>
       </c>
       <c r="T168" s="81">
-        <f>AK168</f>
+        <f>SUM(AK168:AK168)</f>
         <v/>
       </c>
       <c r="Y168" s="81" t="n">
@@ -27532,11 +27532,11 @@
         <v/>
       </c>
       <c r="S169" s="81">
-        <f>AI169</f>
+        <f>SUM(AI169:AI169)</f>
         <v/>
       </c>
       <c r="T169" s="81">
-        <f>AK169</f>
+        <f>SUM(AK169:AK169)</f>
         <v/>
       </c>
       <c r="Y169" s="81" t="n">
@@ -27623,11 +27623,11 @@
         <v/>
       </c>
       <c r="S170" s="81">
-        <f>AI170</f>
+        <f>SUM(AI170:AI170)</f>
         <v/>
       </c>
       <c r="T170" s="81">
-        <f>AK170</f>
+        <f>SUM(AK170:AK170)</f>
         <v/>
       </c>
       <c r="Y170" s="81" t="n">
@@ -27711,11 +27711,11 @@
         <v/>
       </c>
       <c r="S171" s="81">
-        <f>AI171</f>
+        <f>SUM(AI171:AI171)</f>
         <v/>
       </c>
       <c r="T171" s="81">
-        <f>AK171</f>
+        <f>SUM(AK171:AK171)</f>
         <v/>
       </c>
       <c r="Y171" s="81" t="n">
@@ -27802,11 +27802,11 @@
         <v/>
       </c>
       <c r="S172" s="81">
-        <f>AI172</f>
+        <f>SUM(AI172:AI172)</f>
         <v/>
       </c>
       <c r="T172" s="81">
-        <f>AK172</f>
+        <f>SUM(AK172:AK172)</f>
         <v/>
       </c>
       <c r="Y172" s="81" t="n">
@@ -27890,11 +27890,11 @@
         <v/>
       </c>
       <c r="S173" s="81">
-        <f>AI173</f>
+        <f>SUM(AI173:AI173)</f>
         <v/>
       </c>
       <c r="T173" s="81">
-        <f>AK173</f>
+        <f>SUM(AK173:AK173)</f>
         <v/>
       </c>
       <c r="Y173" s="81" t="n">
@@ -27981,11 +27981,11 @@
         <v/>
       </c>
       <c r="S174" s="81">
-        <f>AI174</f>
+        <f>SUM(AI174:AI174)</f>
         <v/>
       </c>
       <c r="T174" s="81">
-        <f>AK174</f>
+        <f>SUM(AK174:AK174)</f>
         <v/>
       </c>
       <c r="Y174" s="81" t="n">
@@ -28072,11 +28072,11 @@
         <v/>
       </c>
       <c r="S175" s="81">
-        <f>AI175</f>
+        <f>SUM(AI175:AI175)</f>
         <v/>
       </c>
       <c r="T175" s="81">
-        <f>AK175</f>
+        <f>SUM(AK175:AK175)</f>
         <v/>
       </c>
       <c r="Y175" s="81" t="n">
@@ -28160,11 +28160,11 @@
         <v/>
       </c>
       <c r="S176" s="81">
-        <f>AI176</f>
+        <f>SUM(AI176:AI176)</f>
         <v/>
       </c>
       <c r="T176" s="81">
-        <f>AK176</f>
+        <f>SUM(AK176:AK176)</f>
         <v/>
       </c>
       <c r="Y176" s="81" t="n">
@@ -28251,11 +28251,11 @@
         <v/>
       </c>
       <c r="S177" s="81">
-        <f>AI177</f>
+        <f>SUM(AI177:AI177)</f>
         <v/>
       </c>
       <c r="T177" s="81">
-        <f>AK177</f>
+        <f>SUM(AK177:AK177)</f>
         <v/>
       </c>
       <c r="Y177" s="81" t="n">
@@ -28342,11 +28342,11 @@
         <v/>
       </c>
       <c r="S178" s="81">
-        <f>AI178</f>
+        <f>SUM(AI178:AI178)</f>
         <v/>
       </c>
       <c r="T178" s="81">
-        <f>AK178</f>
+        <f>SUM(AK178:AK178)</f>
         <v/>
       </c>
       <c r="Y178" s="81" t="n">
@@ -28430,11 +28430,11 @@
         <v/>
       </c>
       <c r="S179" s="81">
-        <f>AI179</f>
+        <f>SUM(AI179:AI179)</f>
         <v/>
       </c>
       <c r="T179" s="81">
-        <f>AK179</f>
+        <f>SUM(AK179:AK179)</f>
         <v/>
       </c>
       <c r="Y179" s="81" t="n">
@@ -28521,11 +28521,11 @@
         <v/>
       </c>
       <c r="S180" s="81">
-        <f>AI180</f>
+        <f>SUM(AI180:AI180)</f>
         <v/>
       </c>
       <c r="T180" s="81">
-        <f>AK180</f>
+        <f>SUM(AK180:AK180)</f>
         <v/>
       </c>
       <c r="Y180" s="81" t="n">
@@ -28609,11 +28609,11 @@
         <v/>
       </c>
       <c r="S181" s="81">
-        <f>AI181</f>
+        <f>SUM(AI181:AI181)</f>
         <v/>
       </c>
       <c r="T181" s="81">
-        <f>AK181</f>
+        <f>SUM(AK181:AK181)</f>
         <v/>
       </c>
       <c r="Y181" s="81" t="n">
@@ -28700,11 +28700,11 @@
         <v/>
       </c>
       <c r="S182" s="81">
-        <f>AI182</f>
+        <f>SUM(AI182:AI182)</f>
         <v/>
       </c>
       <c r="T182" s="81">
-        <f>AK182</f>
+        <f>SUM(AK182:AK182)</f>
         <v/>
       </c>
       <c r="Y182" s="81" t="n">
@@ -28788,11 +28788,11 @@
         <v/>
       </c>
       <c r="S183" s="81">
-        <f>AI183</f>
+        <f>SUM(AI183:AI183)</f>
         <v/>
       </c>
       <c r="T183" s="81">
-        <f>AK183</f>
+        <f>SUM(AK183:AK183)</f>
         <v/>
       </c>
       <c r="Y183" s="81" t="n">
@@ -28876,11 +28876,11 @@
         <v/>
       </c>
       <c r="S184" s="81">
-        <f>AI184</f>
+        <f>SUM(AI184:AI184)</f>
         <v/>
       </c>
       <c r="T184" s="81">
-        <f>AK184</f>
+        <f>SUM(AK184:AK184)</f>
         <v/>
       </c>
       <c r="Y184" s="81" t="n">
@@ -28964,11 +28964,11 @@
         <v/>
       </c>
       <c r="S185" s="81">
-        <f>AI185</f>
+        <f>SUM(AI185:AI185)</f>
         <v/>
       </c>
       <c r="T185" s="81">
-        <f>AK185</f>
+        <f>SUM(AK185:AK185)</f>
         <v/>
       </c>
       <c r="Y185" s="81" t="n">
@@ -29052,11 +29052,11 @@
         <v/>
       </c>
       <c r="S186" s="81">
-        <f>AI186</f>
+        <f>SUM(AI186:AI186)</f>
         <v/>
       </c>
       <c r="T186" s="81">
-        <f>AK186</f>
+        <f>SUM(AK186:AK186)</f>
         <v/>
       </c>
       <c r="Y186" s="81" t="n">
@@ -29143,11 +29143,11 @@
         <v/>
       </c>
       <c r="S187" s="81">
-        <f>AI187</f>
+        <f>SUM(AI187:AI187)</f>
         <v/>
       </c>
       <c r="T187" s="81">
-        <f>AK187</f>
+        <f>SUM(AK187:AK187)</f>
         <v/>
       </c>
       <c r="Y187" s="81" t="n">
@@ -29231,11 +29231,11 @@
         <v/>
       </c>
       <c r="S188" s="81">
-        <f>AI188</f>
+        <f>SUM(AI188:AI188)</f>
         <v/>
       </c>
       <c r="T188" s="81">
-        <f>AK188</f>
+        <f>SUM(AK188:AK188)</f>
         <v/>
       </c>
       <c r="Y188" s="81" t="n">
@@ -29322,11 +29322,11 @@
         <v/>
       </c>
       <c r="S189" s="81">
-        <f>AI189</f>
+        <f>SUM(AI189:AI189)</f>
         <v/>
       </c>
       <c r="T189" s="81">
-        <f>AK189</f>
+        <f>SUM(AK189:AK189)</f>
         <v/>
       </c>
       <c r="Y189" s="81" t="n">
@@ -29416,11 +29416,11 @@
         <v/>
       </c>
       <c r="S190" s="81">
-        <f>AI190</f>
+        <f>SUM(AI190:AI190)</f>
         <v/>
       </c>
       <c r="T190" s="81">
-        <f>AK190</f>
+        <f>SUM(AK190:AK190)</f>
         <v/>
       </c>
       <c r="Y190" s="81" t="n">
@@ -29504,11 +29504,11 @@
         <v/>
       </c>
       <c r="S191" s="81">
-        <f>AI191</f>
+        <f>SUM(AI191:AI191)</f>
         <v/>
       </c>
       <c r="T191" s="81">
-        <f>AK191</f>
+        <f>SUM(AK191:AK191)</f>
         <v/>
       </c>
       <c r="Y191" s="81" t="n">
@@ -29595,11 +29595,11 @@
         <v/>
       </c>
       <c r="S192" s="81">
-        <f>AI192</f>
+        <f>SUM(AI192:AI192)</f>
         <v/>
       </c>
       <c r="T192" s="81">
-        <f>AK192</f>
+        <f>SUM(AK192:AK192)</f>
         <v/>
       </c>
       <c r="Y192" s="81" t="n">
@@ -29686,11 +29686,11 @@
         <v/>
       </c>
       <c r="S193" s="81">
-        <f>AI193</f>
+        <f>SUM(AI193:AI193)</f>
         <v/>
       </c>
       <c r="T193" s="81">
-        <f>AK193</f>
+        <f>SUM(AK193:AK193)</f>
         <v/>
       </c>
       <c r="Y193" s="81" t="n">
@@ -29777,11 +29777,11 @@
         <v/>
       </c>
       <c r="S194" s="81">
-        <f>AI194</f>
+        <f>SUM(AI194:AI194)</f>
         <v/>
       </c>
       <c r="T194" s="81">
-        <f>AK194</f>
+        <f>SUM(AK194:AK194)</f>
         <v/>
       </c>
       <c r="Y194" s="81" t="n">
@@ -29865,11 +29865,11 @@
         <v/>
       </c>
       <c r="S195" s="81">
-        <f>AI195</f>
+        <f>SUM(AI195:AI195)</f>
         <v/>
       </c>
       <c r="T195" s="81">
-        <f>AK195</f>
+        <f>SUM(AK195:AK195)</f>
         <v/>
       </c>
       <c r="Y195" s="81" t="n">
@@ -29956,11 +29956,11 @@
         <v/>
       </c>
       <c r="S196" s="81">
-        <f>AI196</f>
+        <f>SUM(AI196:AI196)</f>
         <v/>
       </c>
       <c r="T196" s="81">
-        <f>AK196</f>
+        <f>SUM(AK196:AK196)</f>
         <v/>
       </c>
       <c r="Y196" s="81" t="n">
@@ -30044,11 +30044,11 @@
         <v/>
       </c>
       <c r="S197" s="81">
-        <f>AI197</f>
+        <f>SUM(AI197:AI197)</f>
         <v/>
       </c>
       <c r="T197" s="81">
-        <f>AK197</f>
+        <f>SUM(AK197:AK197)</f>
         <v/>
       </c>
       <c r="Y197" s="81" t="n">
@@ -30135,11 +30135,11 @@
         <v/>
       </c>
       <c r="S198" s="81">
-        <f>AI198</f>
+        <f>SUM(AI198:AI198)</f>
         <v/>
       </c>
       <c r="T198" s="81">
-        <f>AK198</f>
+        <f>SUM(AK198:AK198)</f>
         <v/>
       </c>
       <c r="Y198" s="81" t="n">
@@ -30226,11 +30226,11 @@
         <v/>
       </c>
       <c r="S199" s="81">
-        <f>AI199</f>
+        <f>SUM(AI199:AI199)</f>
         <v/>
       </c>
       <c r="T199" s="81">
-        <f>AK199</f>
+        <f>SUM(AK199:AK199)</f>
         <v/>
       </c>
       <c r="Y199" s="81" t="n">
@@ -30317,11 +30317,11 @@
         <v/>
       </c>
       <c r="S200" s="81">
-        <f>AI200</f>
+        <f>SUM(AI200:AI200)</f>
         <v/>
       </c>
       <c r="T200" s="81">
-        <f>AK200</f>
+        <f>SUM(AK200:AK200)</f>
         <v/>
       </c>
       <c r="Y200" s="81" t="n">
@@ -30408,11 +30408,11 @@
         <v/>
       </c>
       <c r="S201" s="81">
-        <f>AI201</f>
+        <f>SUM(AI201:AI201)</f>
         <v/>
       </c>
       <c r="T201" s="81">
-        <f>AK201</f>
+        <f>SUM(AK201:AK201)</f>
         <v/>
       </c>
       <c r="Y201" s="81" t="n">
@@ -30502,11 +30502,11 @@
         <v/>
       </c>
       <c r="S202" s="81">
-        <f>AI202</f>
+        <f>SUM(AI202:AI202)</f>
         <v/>
       </c>
       <c r="T202" s="81">
-        <f>AK202</f>
+        <f>SUM(AK202:AK202)</f>
         <v/>
       </c>
       <c r="Y202" s="81" t="n">
@@ -30588,11 +30588,11 @@
         <v/>
       </c>
       <c r="S203" s="85">
-        <f>AI203</f>
+        <f>SUM(AI203:AI203)</f>
         <v/>
       </c>
       <c r="T203" s="85">
-        <f>AK203</f>
+        <f>SUM(AK203:AK203)</f>
         <v/>
       </c>
       <c r="U203" s="86" t="n"/>
@@ -30683,11 +30683,11 @@
         <v/>
       </c>
       <c r="S204" s="81">
-        <f>AI204</f>
+        <f>SUM(AI204:AI204)</f>
         <v/>
       </c>
       <c r="T204" s="81">
-        <f>AK204</f>
+        <f>SUM(AK204:AK204)</f>
         <v/>
       </c>
       <c r="Y204" s="81" t="n">
@@ -30774,11 +30774,11 @@
         <v/>
       </c>
       <c r="S205" s="81">
-        <f>AI205</f>
+        <f>SUM(AI205:AI205)</f>
         <v/>
       </c>
       <c r="T205" s="81">
-        <f>AK205</f>
+        <f>SUM(AK205:AK205)</f>
         <v/>
       </c>
       <c r="Y205" s="81" t="n">
@@ -30862,11 +30862,11 @@
         <v/>
       </c>
       <c r="S206" s="81">
-        <f>AI206</f>
+        <f>SUM(AI206:AI206)</f>
         <v/>
       </c>
       <c r="T206" s="81">
-        <f>AK206</f>
+        <f>SUM(AK206:AK206)</f>
         <v/>
       </c>
       <c r="Y206" s="81" t="n">
@@ -30953,11 +30953,11 @@
         <v/>
       </c>
       <c r="S207" s="81">
-        <f>AI207</f>
+        <f>SUM(AI207:AI207)</f>
         <v/>
       </c>
       <c r="T207" s="81">
-        <f>AK207</f>
+        <f>SUM(AK207:AK207)</f>
         <v/>
       </c>
       <c r="Y207" s="81" t="n">
@@ -31044,11 +31044,11 @@
         <v/>
       </c>
       <c r="S208" s="81">
-        <f>AI208</f>
+        <f>SUM(AI208:AI208)</f>
         <v/>
       </c>
       <c r="T208" s="81">
-        <f>AK208</f>
+        <f>SUM(AK208:AK208)</f>
         <v/>
       </c>
       <c r="Y208" s="81" t="n">
@@ -31132,11 +31132,11 @@
         <v/>
       </c>
       <c r="S209" s="81">
-        <f>AI209</f>
+        <f>SUM(AI209:AI209)</f>
         <v/>
       </c>
       <c r="T209" s="81">
-        <f>AK209</f>
+        <f>SUM(AK209:AK209)</f>
         <v/>
       </c>
       <c r="Y209" s="81" t="n">
@@ -31223,11 +31223,11 @@
         <v/>
       </c>
       <c r="S210" s="81">
-        <f>AI210</f>
+        <f>SUM(AI210:AI210)</f>
         <v/>
       </c>
       <c r="T210" s="81">
-        <f>AK210</f>
+        <f>SUM(AK210:AK210)</f>
         <v/>
       </c>
       <c r="Y210" s="81" t="n">
@@ -31311,11 +31311,11 @@
         <v/>
       </c>
       <c r="S211" s="81">
-        <f>AI211</f>
+        <f>SUM(AI211:AI211)</f>
         <v/>
       </c>
       <c r="T211" s="81">
-        <f>AK211</f>
+        <f>SUM(AK211:AK211)</f>
         <v/>
       </c>
       <c r="Y211" s="81" t="n">
@@ -31402,11 +31402,11 @@
         <v/>
       </c>
       <c r="S212" s="81">
-        <f>AI212</f>
+        <f>SUM(AI212:AI212)</f>
         <v/>
       </c>
       <c r="T212" s="81">
-        <f>AK212</f>
+        <f>SUM(AK212:AK212)</f>
         <v/>
       </c>
       <c r="Y212" s="81" t="n">
